--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_los_lagos.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:38</t>
+    <t xml:space="preserve">2026-09-09 20:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_los_lagos.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_los_lagos.xlsx
@@ -24,96 +24,96 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Castro</t>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">Chonchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frutillar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
-    <t xml:space="preserve">Llanquihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maullín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osorno</t>
-  </si>
-  <si>
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">Puerto Montt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Varas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puqueldón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puyehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quellón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pablo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:41</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="3">
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.86</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="7">
@@ -575,7 +575,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.61</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="8">
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.49</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +591,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="10">
@@ -599,7 +599,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +623,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="14">
@@ -631,7 +631,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.51</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="15">
@@ -639,7 +639,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.23</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16">
@@ -647,7 +647,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="17">
@@ -655,7 +655,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.36</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.22</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="19">
@@ -671,7 +671,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -679,7 +679,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5.8</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="21">
@@ -687,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.62</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="22">
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.59</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23">
@@ -719,7 +719,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1.89</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="26">
@@ -727,7 +727,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.31</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="27">
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="28">
@@ -743,7 +743,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5.07</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="29">
@@ -751,7 +751,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>4.23</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="30">
@@ -759,7 +759,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="31">
@@ -767,7 +767,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
     </row>
   </sheetData>
